--- a/data/trans_orig/P5705-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P5705-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de recibir amor y afecto en 2007</t>
+          <t>Población según la frecuencia de recibir amor y afecto en 2007 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>521664</t>
+          <t>517684</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>583017</t>
+          <t>582501</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>50,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,51%</t>
+          <t>56,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>650713</t>
+          <t>648879</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>722042</t>
+          <t>720930</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>49,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>54,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1190882</t>
+          <t>1188058</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1282932</t>
+          <t>1283635</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>50,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>54,7%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>242305</t>
+          <t>243669</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>298485</t>
+          <t>301448</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>323619</t>
+          <t>326037</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>386864</t>
+          <t>386291</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>583001</t>
+          <t>586505</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>667608</t>
+          <t>673137</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,68%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>121669</t>
+          <t>120400</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>165993</t>
+          <t>164965</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>169566</t>
+          <t>171416</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>220775</t>
+          <t>221146</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>303361</t>
+          <t>302736</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>367271</t>
+          <t>369294</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,74%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45441</t>
+          <t>46395</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>76837</t>
+          <t>77124</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>55933</t>
+          <t>56281</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>89707</t>
+          <t>89808</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>107140</t>
+          <t>109854</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>150645</t>
+          <t>151254</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,45%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3565</t>
+          <t>3355</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16772</t>
+          <t>16443</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5096</t>
+          <t>4774</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18177</t>
+          <t>17146</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>11474</t>
+          <t>10941</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>30197</t>
+          <t>28974</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1053681</t>
+          <t>1049199</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1129510</t>
+          <t>1132744</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>61,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>66,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>948192</t>
+          <t>953118</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1028523</t>
+          <t>1029152</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>60,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>64,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2024553</t>
+          <t>2021962</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2135939</t>
+          <t>2134362</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>61,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>65,09%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>417798</t>
+          <t>416787</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>490102</t>
+          <t>490949</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>401114</t>
+          <t>399558</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>475102</t>
+          <t>472117</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>841394</t>
+          <t>841482</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>947589</t>
+          <t>941674</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,72%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>101900</t>
+          <t>103457</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>147319</t>
+          <t>146177</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>108380</t>
+          <t>109920</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>152047</t>
+          <t>152510</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>220949</t>
+          <t>220450</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>280608</t>
+          <t>283707</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,65%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13528</t>
+          <t>13705</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32509</t>
+          <t>31478</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18767</t>
+          <t>19912</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42019</t>
+          <t>41983</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>36148</t>
+          <t>38377</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>66282</t>
+          <t>68043</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9122</t>
+          <t>9325</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8292</t>
+          <t>7188</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1067</t>
+          <t>1237</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10725</t>
+          <t>12335</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,38%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>339798</t>
+          <t>337077</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>384808</t>
+          <t>381887</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>61,62%</t>
+          <t>61,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>69,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>296354</t>
+          <t>299497</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>338535</t>
+          <t>339443</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>62,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,06%</t>
+          <t>71,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>649292</t>
+          <t>647525</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>712993</t>
+          <t>711455</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>63,17%</t>
+          <t>63,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>69,22%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>118628</t>
+          <t>120388</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>160294</t>
+          <t>161356</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>100024</t>
+          <t>100616</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>139970</t>
+          <t>138646</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>230274</t>
+          <t>230847</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>286323</t>
+          <t>287204</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,94%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>29741</t>
+          <t>29382</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>55555</t>
+          <t>55400</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>19832</t>
+          <t>19592</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>42262</t>
+          <t>40899</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>54143</t>
+          <t>54340</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>88030</t>
+          <t>88048</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,57%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3690</t>
+          <t>4201</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18002</t>
+          <t>18009</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>4543</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17519</t>
+          <t>17878</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10948</t>
+          <t>10842</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30408</t>
+          <t>29431</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4227</t>
+          <t>3386</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,62 +2584,62 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>834</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>4156</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>834</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>4193</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1949335</t>
+          <t>1949999</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2059542</t>
+          <t>2062645</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1940706</t>
+          <t>1938915</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2052893</t>
+          <t>2052968</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>57,46%</t>
+          <t>57,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3915963</t>
+          <t>3924467</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4081276</t>
+          <t>4080680</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>58,85%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>61,33%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>817107</t>
+          <t>813580</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>919053</t>
+          <t>919511</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>856758</t>
+          <t>855486</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>956912</t>
+          <t>958506</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1702049</t>
+          <t>1707370</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1835490</t>
+          <t>1843269</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,7%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>276139</t>
+          <t>272018</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>341793</t>
+          <t>339313</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>317852</t>
+          <t>317611</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>392246</t>
+          <t>387759</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>606846</t>
+          <t>606196</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>707426</t>
+          <t>706554</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,62%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>72955</t>
+          <t>73232</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>112542</t>
+          <t>112826</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>90036</t>
+          <t>90456</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>132610</t>
+          <t>131084</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>173724</t>
+          <t>169916</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>232393</t>
+          <t>229169</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5676</t>
+          <t>5647</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>20738</t>
+          <t>20247</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>7009</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>20812</t>
+          <t>21022</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>15623</t>
+          <t>15138</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>35678</t>
+          <t>35077</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de recibir amor y afecto en 2012</t>
+          <t>Población según la frecuencia de recibir amor y afecto en 2012 (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>553062</t>
+          <t>552181</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>614573</t>
+          <t>614252</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,51%</t>
+          <t>63,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>743903</t>
+          <t>743448</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>820146</t>
+          <t>820110</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3742,7 +3742,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>55,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1319439</t>
+          <t>1316929</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1421157</t>
+          <t>1412577</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>61,78%</t>
+          <t>61,41%</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>230192</t>
+          <t>229690</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>285974</t>
+          <t>285587</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>355942</t>
+          <t>355033</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>427778</t>
+          <t>426250</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>602962</t>
+          <t>604289</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>691697</t>
+          <t>690529</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,02%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>77925</t>
+          <t>80753</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>115560</t>
+          <t>118837</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>101555</t>
+          <t>100823</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>146857</t>
+          <t>146048</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>188722</t>
+          <t>192184</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>248597</t>
+          <t>250065</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,87%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12261</t>
+          <t>12528</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30183</t>
+          <t>30041</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18350</t>
+          <t>18771</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39704</t>
+          <t>39958</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>36036</t>
+          <t>35527</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>63293</t>
+          <t>62687</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4178</t>
+          <t>4551</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17809</t>
+          <t>19320</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4159,47 +4159,47 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>10876</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>5748</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>19673</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
           <t>0,43%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>10876</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>5816</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>18794</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>13514</t>
+          <t>12822</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>32136</t>
+          <t>31920</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1296739</t>
+          <t>1294266</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1378754</t>
+          <t>1385364</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>65,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1107574</t>
+          <t>1104544</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1187955</t>
+          <t>1187257</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>67,7%</t>
+          <t>67,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2426365</t>
+          <t>2432056</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2548531</t>
+          <t>2546729</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>65,29%</t>
+          <t>65,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>68,53%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>418185</t>
+          <t>418133</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>495827</t>
+          <t>493921</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>417443</t>
+          <t>415104</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>494831</t>
+          <t>491448</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>849197</t>
+          <t>853366</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>961255</t>
+          <t>963905</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,94%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>120378</t>
+          <t>119827</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>166284</t>
+          <t>167948</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>102713</t>
+          <t>99764</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>145181</t>
+          <t>143488</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>232938</t>
+          <t>236202</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>301277</t>
+          <t>301112</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,1%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12973</t>
+          <t>13635</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33089</t>
+          <t>34728</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15099</t>
+          <t>15467</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35745</t>
+          <t>39430</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33937</t>
+          <t>33037</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>64359</t>
+          <t>63606</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>880</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8026</t>
+          <t>7488</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2948</t>
+          <t>2156</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13519</t>
+          <t>13218</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4320</t>
+          <t>5038</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>17730</t>
+          <t>17303</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>305197</t>
+          <t>304023</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>349223</t>
+          <t>350763</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>63,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>299204</t>
+          <t>300617</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>340104</t>
+          <t>340238</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>65,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>616464</t>
+          <t>617964</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>681331</t>
+          <t>678617</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>65,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>72,46%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>103209</t>
+          <t>102293</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>142722</t>
+          <t>144755</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>99965</t>
+          <t>100227</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>139268</t>
+          <t>137227</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>211146</t>
+          <t>212405</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>271465</t>
+          <t>268824</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>28,7%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13108</t>
+          <t>12730</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>33024</t>
+          <t>33832</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10974</t>
+          <t>10345</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>28582</t>
+          <t>28850</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>26976</t>
+          <t>28073</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>53355</t>
+          <t>54494</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9620</t>
+          <t>9197</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4828</t>
+          <t>5501</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1957</t>
+          <t>1944</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10825</t>
+          <t>11041</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11668</t>
+          <t>11469</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5543,62 +5543,62 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>3397</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>2132</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>3397</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>13344</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2193443</t>
+          <t>2195709</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2307182</t>
+          <t>2311552</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>64,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>67,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2192275</t>
+          <t>2194433</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2312485</t>
+          <t>2312143</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>61,85%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,24%</t>
+          <t>65,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4423350</t>
+          <t>4421791</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4591580</t>
+          <t>4583109</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>66,04%</t>
+          <t>65,91%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>785416</t>
+          <t>781491</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>890808</t>
+          <t>884724</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>909079</t>
+          <t>908993</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1019592</t>
+          <t>1014627</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1723632</t>
+          <t>1723383</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1867728</t>
+          <t>1867498</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>226689</t>
+          <t>231290</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>292881</t>
+          <t>297947</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>232934</t>
+          <t>230343</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>299843</t>
+          <t>295265</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>478501</t>
+          <t>478888</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>567126</t>
+          <t>569059</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,18%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>32918</t>
+          <t>32626</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>59823</t>
+          <t>60763</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>38779</t>
+          <t>40212</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>70040</t>
+          <t>71564</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>82123</t>
+          <t>79185</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>123116</t>
+          <t>120773</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8712</t>
+          <t>9085</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>26738</t>
+          <t>27086</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>10361</t>
+          <t>10193</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>27531</t>
+          <t>27422</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6245,7 +6245,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>22048</t>
+          <t>22862</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>46635</t>
+          <t>46739</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6275,7 +6275,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6456,7 +6456,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de recibir amor y afecto en 2016</t>
+          <t>Población según la frecuencia de recibir amor y afecto en 2016 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6651,12 +6651,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>335161</t>
+          <t>333910</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>388766</t>
+          <t>387436</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>44,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>51,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>442296</t>
+          <t>441963</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>507913</t>
+          <t>508207</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>44,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,13%</t>
+          <t>51,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>791711</t>
+          <t>792271</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>875944</t>
+          <t>877447</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>50,24%</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>221200</t>
+          <t>221176</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>271055</t>
+          <t>270128</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>287722</t>
+          <t>288675</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>347693</t>
+          <t>348648</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>523392</t>
+          <t>526076</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>605528</t>
+          <t>604455</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>34,61%</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>87635</t>
+          <t>86576</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>126811</t>
+          <t>125177</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>138498</t>
+          <t>134554</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>185971</t>
+          <t>185841</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>231917</t>
+          <t>237334</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>296856</t>
+          <t>297268</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,02%</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23421</t>
+          <t>23139</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45516</t>
+          <t>45204</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20272</t>
+          <t>20728</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43256</t>
+          <t>42037</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7040,12 +7040,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>49170</t>
+          <t>48843</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>80396</t>
+          <t>81611</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3836</t>
+          <t>3943</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16053</t>
+          <t>15665</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4823</t>
+          <t>4789</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>20018</t>
+          <t>21481</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>11758</t>
+          <t>11668</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>30488</t>
+          <t>30307</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1099386</t>
+          <t>1096332</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1191365</t>
+          <t>1193751</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7348,12 +7348,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>53,04%</t>
+          <t>52,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>57,47%</t>
+          <t>57,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>995089</t>
+          <t>995234</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1084415</t>
+          <t>1088531</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2123561</t>
+          <t>2123969</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2252671</t>
+          <t>2251568</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>52,36%</t>
+          <t>52,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,54%</t>
+          <t>55,52%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>608407</t>
+          <t>603973</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>697331</t>
+          <t>693763</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>630250</t>
+          <t>627597</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>717103</t>
+          <t>715958</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1257687</t>
+          <t>1257802</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1385468</t>
+          <t>1377302</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7536,7 +7536,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>33,96%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>202949</t>
+          <t>202868</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>261717</t>
+          <t>261180</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>208293</t>
+          <t>207708</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>265644</t>
+          <t>270727</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>426422</t>
+          <t>430485</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>508008</t>
+          <t>510035</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24530</t>
+          <t>24501</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>49211</t>
+          <t>50869</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7692,7 +7692,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19305</t>
+          <t>19737</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42736</t>
+          <t>42175</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>50504</t>
+          <t>50078</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>86162</t>
+          <t>82519</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5425</t>
+          <t>5374</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18919</t>
+          <t>17920</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7805,7 +7805,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10832</t>
+          <t>11678</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7840,7 +7840,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8982</t>
+          <t>9359</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>26396</t>
+          <t>24844</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,61%</t>
         </is>
       </c>
     </row>
@@ -8015,12 +8015,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>311037</t>
+          <t>309023</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>359047</t>
+          <t>357586</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8030,12 +8030,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>56,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>65,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>314407</t>
+          <t>309977</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>359232</t>
+          <t>357550</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>56,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>634980</t>
+          <t>639872</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>700446</t>
+          <t>702916</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>58,21%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>64,21%</t>
+          <t>64,43%</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>131800</t>
+          <t>132844</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>174807</t>
+          <t>175596</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>132843</t>
+          <t>134028</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>176545</t>
+          <t>175521</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>273580</t>
+          <t>274429</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>336150</t>
+          <t>335063</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,71%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>43087</t>
+          <t>41334</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>70466</t>
+          <t>71303</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>35370</t>
+          <t>34813</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>62508</t>
+          <t>62855</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>84774</t>
+          <t>82701</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>125476</t>
+          <t>125730</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,53%</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8197</t>
+          <t>9142</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8369,12 +8369,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2096</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12822</t>
+          <t>12394</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4067</t>
+          <t>4868</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16190</t>
+          <t>17315</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -8472,7 +8472,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4878</t>
+          <t>5008</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8507,7 +8507,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9033</t>
+          <t>7327</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8522,7 +8522,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8542,7 +8542,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10542</t>
+          <t>11102</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8557,7 +8557,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1786391</t>
+          <t>1781710</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1902970</t>
+          <t>1897963</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>52,98%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>56,43%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1794642</t>
+          <t>1785960</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1916290</t>
+          <t>1907801</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8747,12 +8747,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>50,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>54,42%</t>
+          <t>54,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3610618</t>
+          <t>3613062</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3778095</t>
+          <t>3779327</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8782,12 +8782,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>52,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>54,83%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>992271</t>
+          <t>995526</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1101910</t>
+          <t>1104732</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1087580</t>
+          <t>1088537</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1196468</t>
+          <t>1202739</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2104090</t>
+          <t>2103837</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2265334</t>
+          <t>2265466</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8900,7 +8900,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,87%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>350322</t>
+          <t>350412</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>431106</t>
+          <t>427780</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>405561</t>
+          <t>404923</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>486095</t>
+          <t>486007</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>781516</t>
+          <t>781117</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>897361</t>
+          <t>894847</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,98%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>57103</t>
+          <t>55906</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>90497</t>
+          <t>90536</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9051,7 +9051,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>50875</t>
+          <t>50031</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>84105</t>
+          <t>82645</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9086,12 +9086,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>113097</t>
+          <t>113787</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>162745</t>
+          <t>162353</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,7 +9121,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>13030</t>
+          <t>12699</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>30371</t>
+          <t>31214</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>10089</t>
+          <t>9670</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>30747</t>
+          <t>27705</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>26492</t>
+          <t>26344</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>50652</t>
+          <t>51633</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9239,7 +9239,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -9415,7 +9415,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de recibir amor y afecto en 2023</t>
+          <t>Población según la frecuencia de recibir amor y afecto en 2023 (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9610,12 +9610,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>259840</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>299133</t>
+          <t>300239</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9625,12 +9625,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>50,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>58,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9645,12 +9645,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>366587</t>
+          <t>365857</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>408926</t>
+          <t>409722</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9660,12 +9660,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>48,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>54,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9680,12 +9680,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>635509</t>
+          <t>638087</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>697229</t>
+          <t>696965</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9695,12 +9695,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>50,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>55,06%</t>
         </is>
       </c>
     </row>
@@ -9723,12 +9723,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>116327</t>
+          <t>114791</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>157154</t>
+          <t>151328</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9738,12 +9738,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9758,12 +9758,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>194300</t>
+          <t>192906</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>232174</t>
+          <t>232896</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9773,12 +9773,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9793,12 +9793,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>321878</t>
+          <t>319374</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>375897</t>
+          <t>374727</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9808,12 +9808,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,6%</t>
         </is>
       </c>
     </row>
@@ -9836,12 +9836,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>41577</t>
+          <t>42592</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>66782</t>
+          <t>66046</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9851,12 +9851,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9871,12 +9871,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>76712</t>
+          <t>76499</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>103524</t>
+          <t>103515</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9886,7 +9886,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -9906,12 +9906,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>124384</t>
+          <t>126328</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>160736</t>
+          <t>160965</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9921,12 +9921,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,72%</t>
         </is>
       </c>
     </row>
@@ -9949,12 +9949,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23256</t>
+          <t>23699</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42897</t>
+          <t>42752</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9964,12 +9964,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9984,12 +9984,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37774</t>
+          <t>38035</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>60027</t>
+          <t>61745</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9999,12 +9999,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10019,12 +10019,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>65302</t>
+          <t>66696</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>93656</t>
+          <t>93998</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9504</t>
+          <t>8796</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>22501</t>
+          <t>21621</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11044</t>
+          <t>11185</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>22524</t>
+          <t>23518</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>22704</t>
+          <t>22251</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>40222</t>
+          <t>39713</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -10292,12 +10292,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1447519</t>
+          <t>1440979</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1777642</t>
+          <t>1751840</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10307,12 +10307,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>63,27%</t>
+          <t>62,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10327,12 +10327,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>903289</t>
+          <t>966146</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1445498</t>
+          <t>1443304</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10342,12 +10342,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>43,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>64,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10362,12 +10362,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2443003</t>
+          <t>2487559</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3073107</t>
+          <t>3097399</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10377,12 +10377,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>54,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>68,47%</t>
         </is>
       </c>
     </row>
@@ -10405,12 +10405,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>389646</t>
+          <t>394475</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>643814</t>
+          <t>645196</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10420,12 +10420,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10440,12 +10440,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>599423</t>
+          <t>602236</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1194380</t>
+          <t>1126868</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10455,12 +10455,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>50,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10475,12 +10475,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1121578</t>
+          <t>1113002</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1818996</t>
+          <t>1816966</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10490,12 +10490,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>40,16%</t>
         </is>
       </c>
     </row>
@@ -10518,12 +10518,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>69998</t>
+          <t>71122</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>122787</t>
+          <t>123394</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10553,12 +10553,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>79749</t>
+          <t>80880</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>133762</t>
+          <t>132138</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10588,12 +10588,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>165526</t>
+          <t>163886</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>241933</t>
+          <t>242369</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -10631,12 +10631,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>43988</t>
+          <t>42764</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>80326</t>
+          <t>81171</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10646,12 +10646,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10666,12 +10666,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>41683</t>
+          <t>40041</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>73136</t>
+          <t>74494</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10701,12 +10701,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>93381</t>
+          <t>93948</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>142727</t>
+          <t>147273</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9302</t>
+          <t>9360</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25641</t>
+          <t>26416</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10764,7 +10764,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6137</t>
+          <t>6413</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>17210</t>
+          <t>17292</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>17809</t>
+          <t>16923</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>36797</t>
+          <t>36999</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>421725</t>
+          <t>420695</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>470590</t>
+          <t>470822</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>65,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>72,78%</t>
+          <t>72,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>457720</t>
+          <t>460327</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>497182</t>
+          <t>498835</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>69,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>895017</t>
+          <t>891256</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>953225</t>
+          <t>957133</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>68,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>73,23%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>140129</t>
+          <t>139775</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>184559</t>
+          <t>185860</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>122322</t>
+          <t>122358</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>160287</t>
+          <t>155760</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>274066</t>
+          <t>271272</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>331390</t>
+          <t>329704</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,22%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16221</t>
+          <t>17014</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>36799</t>
+          <t>35169</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>21440</t>
+          <t>21148</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>42287</t>
+          <t>43588</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>41940</t>
+          <t>41896</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>71822</t>
+          <t>71145</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11290,7 +11290,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -11313,12 +11313,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3966</t>
+          <t>4372</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13842</t>
+          <t>13829</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11328,7 +11328,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -11348,12 +11348,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3440</t>
+          <t>3534</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10891</t>
+          <t>11549</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8942</t>
+          <t>9107</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21038</t>
+          <t>21091</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11398,7 +11398,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -11426,12 +11426,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2819</t>
+          <t>2864</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14950</t>
+          <t>14801</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11446,7 +11446,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11461,12 +11461,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>2415</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9693</t>
+          <t>9918</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6800</t>
+          <t>6975</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>20363</t>
+          <t>20646</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2163858</t>
+          <t>2164799</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2549592</t>
+          <t>2551024</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>62,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>73,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1776740</t>
+          <t>1757351</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2315889</t>
+          <t>2319759</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4073316</t>
+          <t>4009285</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4700042</t>
+          <t>4694795</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>56,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>66,16%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>660245</t>
+          <t>656109</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>942725</t>
+          <t>939500</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>945101</t>
+          <t>945795</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1572434</t>
+          <t>1592272</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1753688</t>
+          <t>1765463</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2410960</t>
+          <t>2538313</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>35,77%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>134219</t>
+          <t>140465</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>205314</t>
+          <t>206732</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>181952</t>
+          <t>185762</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>256932</t>
+          <t>256992</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11932,7 +11932,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>352350</t>
+          <t>349176</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>448606</t>
+          <t>450448</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>79273</t>
+          <t>77337</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>124595</t>
+          <t>123278</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12010,12 +12010,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12030,12 +12030,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>89352</t>
+          <t>90330</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>131537</t>
+          <t>132068</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12065,12 +12065,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>182715</t>
+          <t>178814</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>245769</t>
+          <t>242098</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -12108,12 +12108,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>26699</t>
+          <t>25241</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>50766</t>
+          <t>49748</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12123,12 +12123,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>23948</t>
+          <t>23042</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>42234</t>
+          <t>41215</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12158,12 +12158,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12178,12 +12178,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>54196</t>
+          <t>55282</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>85798</t>
+          <t>88224</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12193,12 +12193,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P5705-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P5705-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>517684</t>
+          <t>520319</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>582501</t>
+          <t>583334</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>50,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,46%</t>
+          <t>56,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>648879</t>
+          <t>648876</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>720930</t>
+          <t>719853</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>54,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1188058</t>
+          <t>1189493</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1283635</t>
+          <t>1284113</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>54,72%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>243669</t>
+          <t>241285</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>301448</t>
+          <t>298580</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>326037</t>
+          <t>323251</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>386291</t>
+          <t>383957</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>586505</t>
+          <t>585371</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>673137</t>
+          <t>670874</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,59%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>120400</t>
+          <t>119557</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>164965</t>
+          <t>165771</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>171416</t>
+          <t>170631</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>221146</t>
+          <t>223891</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>302736</t>
+          <t>303754</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>369294</t>
+          <t>371073</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,81%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>46395</t>
+          <t>46614</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>77124</t>
+          <t>77232</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>56281</t>
+          <t>55845</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>89808</t>
+          <t>88974</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>109854</t>
+          <t>108148</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>151254</t>
+          <t>151360</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3355</t>
+          <t>3489</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16443</t>
+          <t>16401</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4774</t>
+          <t>4830</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17146</t>
+          <t>17824</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>10941</t>
+          <t>11814</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>28974</t>
+          <t>29858</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1049199</t>
+          <t>1052333</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1132744</t>
+          <t>1134107</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>61,96%</t>
+          <t>62,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>66,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>953118</t>
+          <t>951408</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1029152</t>
+          <t>1031412</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>65,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2021962</t>
+          <t>2022285</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2134362</t>
+          <t>2134476</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>61,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>416787</t>
+          <t>415047</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>490949</t>
+          <t>489862</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>399558</t>
+          <t>399350</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>472117</t>
+          <t>471608</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>841482</t>
+          <t>840785</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>941674</t>
+          <t>946189</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,86%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>103457</t>
+          <t>101432</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>146177</t>
+          <t>144124</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>109920</t>
+          <t>108818</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>152510</t>
+          <t>153554</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>220450</t>
+          <t>222427</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>283707</t>
+          <t>285350</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,7%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13705</t>
+          <t>14445</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31478</t>
+          <t>33619</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19912</t>
+          <t>19491</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41983</t>
+          <t>46146</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38377</t>
+          <t>37522</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>68043</t>
+          <t>67099</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9325</t>
+          <t>8955</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7188</t>
+          <t>9171</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1237</t>
+          <t>1227</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12335</t>
+          <t>11621</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,35%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>337077</t>
+          <t>337372</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>381887</t>
+          <t>384109</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>61,13%</t>
+          <t>61,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>69,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>299497</t>
+          <t>298410</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>339443</t>
+          <t>338587</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>647525</t>
+          <t>649376</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>711455</t>
+          <t>714673</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>63,0%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>69,53%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>120388</t>
+          <t>119844</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>161356</t>
+          <t>161508</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>100616</t>
+          <t>101173</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>138646</t>
+          <t>139454</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>230847</t>
+          <t>228134</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>287204</t>
+          <t>285546</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>27,78%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>29382</t>
+          <t>28776</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>55400</t>
+          <t>55249</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>19592</t>
+          <t>20542</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40899</t>
+          <t>42174</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,47 +2373,47 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
+          <t>8,85%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>69559</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>54374</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>88186</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>6,77%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>5,29%</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
           <t>8,58%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>69559</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>54340</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>88048</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>6,77%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>5,29%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
-        <is>
-          <t>8,57%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4201</t>
+          <t>4339</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18009</t>
+          <t>18027</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4543</t>
+          <t>4049</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17878</t>
+          <t>18764</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10842</t>
+          <t>11422</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>29431</t>
+          <t>30711</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3386</t>
+          <t>4183</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4156</t>
+          <t>5339</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1949999</t>
+          <t>1945701</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2062645</t>
+          <t>2064243</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>63,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1938915</t>
+          <t>1935619</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2052968</t>
+          <t>2049435</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>57,41%</t>
+          <t>57,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>60,79%</t>
+          <t>60,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3924467</t>
+          <t>3916701</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4080680</t>
+          <t>4081965</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>58,98%</t>
+          <t>58,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>61,33%</t>
+          <t>61,35%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>813580</t>
+          <t>814065</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>919511</t>
+          <t>918249</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>855486</t>
+          <t>857140</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>958506</t>
+          <t>960851</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1707370</t>
+          <t>1705421</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1843269</t>
+          <t>1847264</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,76%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>272018</t>
+          <t>272134</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>339313</t>
+          <t>341723</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>317611</t>
+          <t>317970</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>387759</t>
+          <t>390440</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>606196</t>
+          <t>611509</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>706554</t>
+          <t>711981</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,7%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>73232</t>
+          <t>72529</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>112826</t>
+          <t>110149</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>90456</t>
+          <t>89766</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>131084</t>
+          <t>131246</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>169916</t>
+          <t>174891</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>229169</t>
+          <t>232929</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5647</t>
+          <t>5383</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>20247</t>
+          <t>21470</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,49 +3246,49 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>12346</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>6488</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>20921</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
           <t>0,62%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>12346</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>6285</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>21022</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>22</t>
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>15138</t>
+          <t>15601</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>35077</t>
+          <t>36255</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>552181</t>
+          <t>554326</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>614252</t>
+          <t>616193</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>57,06%</t>
+          <t>57,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,47%</t>
+          <t>63,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>743448</t>
+          <t>740477</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>820110</t>
+          <t>815835</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3742,47 +3742,47 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
+          <t>61,22%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1276</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1365783</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>1319024</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>1415722</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>59,37%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>57,34%</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
           <t>61,54%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1276</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1365783</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>1316929</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1412577</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>59,37%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>57,25%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>61,41%</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>229690</t>
+          <t>227593</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>285587</t>
+          <t>284968</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>355033</t>
+          <t>358597</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>426250</t>
+          <t>425760</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>604289</t>
+          <t>602505</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>690529</t>
+          <t>692745</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>30,12%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>80753</t>
+          <t>79820</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>118837</t>
+          <t>118816</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>100823</t>
+          <t>101533</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>146048</t>
+          <t>146450</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>192184</t>
+          <t>191443</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>250065</t>
+          <t>247361</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,75%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12528</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30041</t>
+          <t>29170</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18771</t>
+          <t>19389</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39958</t>
+          <t>41086</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35527</t>
+          <t>35293</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>62687</t>
+          <t>63925</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4551</t>
+          <t>4565</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19320</t>
+          <t>18082</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4164,7 +4164,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5748</t>
+          <t>5811</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>19673</t>
+          <t>18327</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12822</t>
+          <t>13346</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>31920</t>
+          <t>32296</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1294266</t>
+          <t>1297140</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1385364</t>
+          <t>1383962</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>65,98%</t>
+          <t>66,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>70,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1104544</t>
+          <t>1107359</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1187257</t>
+          <t>1188949</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>67,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2432056</t>
+          <t>2430848</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2546729</t>
+          <t>2544026</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>65,44%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>68,53%</t>
+          <t>68,45%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>418133</t>
+          <t>419817</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>493921</t>
+          <t>492622</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>415104</t>
+          <t>413503</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>491448</t>
+          <t>489097</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>853366</t>
+          <t>855607</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>963905</t>
+          <t>959800</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>25,83%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>119827</t>
+          <t>120107</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>167948</t>
+          <t>167573</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>99764</t>
+          <t>101666</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>143488</t>
+          <t>148810</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>236202</t>
+          <t>232567</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>301112</t>
+          <t>298120</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,02%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13635</t>
+          <t>13454</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34728</t>
+          <t>34892</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15467</t>
+          <t>15437</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39430</t>
+          <t>36437</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33037</t>
+          <t>33026</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>63606</t>
+          <t>61454</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>875</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7488</t>
+          <t>7625</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2156</t>
+          <t>2246</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13218</t>
+          <t>13685</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5038</t>
+          <t>4250</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>17303</t>
+          <t>17807</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>304023</t>
+          <t>306103</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>350763</t>
+          <t>349863</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>63,46%</t>
+          <t>63,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>300617</t>
+          <t>300321</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>340238</t>
+          <t>340780</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>65,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>74,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>617964</t>
+          <t>617930</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>678617</t>
+          <t>679240</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>72,53%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>102293</t>
+          <t>102671</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>144755</t>
+          <t>143735</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>100227</t>
+          <t>100015</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>137227</t>
+          <t>137894</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>212405</t>
+          <t>212023</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>268824</t>
+          <t>269668</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,79%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12730</t>
+          <t>13434</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>33832</t>
+          <t>33663</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10345</t>
+          <t>10151</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>28850</t>
+          <t>27111</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>28073</t>
+          <t>28155</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>54494</t>
+          <t>52532</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9197</t>
+          <t>10025</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5501</t>
+          <t>5844</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1944</t>
+          <t>1954</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11041</t>
+          <t>11823</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11469</t>
+          <t>11230</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14101</t>
+          <t>13726</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2195709</t>
+          <t>2193634</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2311552</t>
+          <t>2308852</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>64,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>67,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2194433</t>
+          <t>2193155</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2312143</t>
+          <t>2306041</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>61,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,23%</t>
+          <t>65,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4421791</t>
+          <t>4413681</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4583109</t>
+          <t>4585126</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>63,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>65,94%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>781491</t>
+          <t>782884</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>884724</t>
+          <t>886989</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>908993</t>
+          <t>904269</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1014627</t>
+          <t>1016456</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1723383</t>
+          <t>1725254</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1867498</t>
+          <t>1872317</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,93%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>231290</t>
+          <t>230874</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>297947</t>
+          <t>296370</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>230343</t>
+          <t>229724</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>295265</t>
+          <t>297390</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>478888</t>
+          <t>477466</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>569059</t>
+          <t>569785</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,19%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>32626</t>
+          <t>32434</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>60763</t>
+          <t>61954</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>40212</t>
+          <t>39889</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>71564</t>
+          <t>70890</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>79185</t>
+          <t>78518</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>120773</t>
+          <t>121440</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9085</t>
+          <t>9224</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>27086</t>
+          <t>26248</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>10193</t>
+          <t>10060</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>27422</t>
+          <t>26705</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>22862</t>
+          <t>23069</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>46739</t>
+          <t>47885</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6280,7 +6280,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,69%</t>
         </is>
       </c>
     </row>
@@ -6651,12 +6651,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>333910</t>
+          <t>332783</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>387436</t>
+          <t>386513</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>51,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>441963</t>
+          <t>444746</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>508207</t>
+          <t>509035</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>792271</t>
+          <t>791131</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>877447</t>
+          <t>877661</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>45,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>50,25%</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>221176</t>
+          <t>220016</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>270128</t>
+          <t>269675</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>288675</t>
+          <t>287225</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>348648</t>
+          <t>346864</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>526076</t>
+          <t>521993</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>604455</t>
+          <t>605679</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>34,68%</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>86576</t>
+          <t>87658</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>125177</t>
+          <t>124284</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>134554</t>
+          <t>136012</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>185841</t>
+          <t>187566</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>237334</t>
+          <t>236342</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>297268</t>
+          <t>294595</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>16,87%</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23139</t>
+          <t>23483</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45204</t>
+          <t>45027</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20728</t>
+          <t>20371</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>42037</t>
+          <t>43355</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7040,12 +7040,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>48843</t>
+          <t>47992</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>81611</t>
+          <t>78977</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3943</t>
+          <t>3911</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15665</t>
+          <t>17124</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4789</t>
+          <t>4607</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21481</t>
+          <t>20239</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>11668</t>
+          <t>10976</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>30307</t>
+          <t>29937</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1096332</t>
+          <t>1100789</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1193751</t>
+          <t>1195768</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7348,12 +7348,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>53,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>57,59%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>995234</t>
+          <t>995206</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1088531</t>
+          <t>1082399</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>54,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2123969</t>
+          <t>2118615</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2251568</t>
+          <t>2249909</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,52%</t>
+          <t>55,48%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>603973</t>
+          <t>602051</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>693763</t>
+          <t>692057</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>627597</t>
+          <t>628527</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>715958</t>
+          <t>712999</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1257802</t>
+          <t>1261081</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1377302</t>
+          <t>1384247</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>34,13%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>202868</t>
+          <t>202140</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>261180</t>
+          <t>260156</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>207708</t>
+          <t>207050</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>270727</t>
+          <t>266149</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>430485</t>
+          <t>425490</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>510035</t>
+          <t>508154</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,53%</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24501</t>
+          <t>25587</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50869</t>
+          <t>51158</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19737</t>
+          <t>20145</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42175</t>
+          <t>42420</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>50078</t>
+          <t>49611</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>82519</t>
+          <t>83277</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5374</t>
+          <t>5060</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17920</t>
+          <t>18499</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2056</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11678</t>
+          <t>12387</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7840,7 +7840,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9359</t>
+          <t>8398</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>24844</t>
+          <t>24917</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7870,7 +7870,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -8015,12 +8015,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>309023</t>
+          <t>305553</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>357586</t>
+          <t>356186</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8030,12 +8030,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>56,6%</t>
+          <t>55,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>65,49%</t>
+          <t>65,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>309977</t>
+          <t>311419</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>357550</t>
+          <t>358509</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>56,89%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>639872</t>
+          <t>637369</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>702916</t>
+          <t>703097</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>58,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>64,43%</t>
+          <t>64,45%</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>132844</t>
+          <t>129056</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>175596</t>
+          <t>172845</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>134028</t>
+          <t>133454</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>175521</t>
+          <t>175663</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>274429</t>
+          <t>275044</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>335063</t>
+          <t>338578</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>31,04%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>41334</t>
+          <t>42623</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>71303</t>
+          <t>72522</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>34813</t>
+          <t>36818</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>62855</t>
+          <t>62496</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>82701</t>
+          <t>83978</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>125730</t>
+          <t>126603</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,61%</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9142</t>
+          <t>8815</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8369,12 +8369,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>1978</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12394</t>
+          <t>12328</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4868</t>
+          <t>4070</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17315</t>
+          <t>17130</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -8472,7 +8472,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5008</t>
+          <t>4480</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8507,7 +8507,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7327</t>
+          <t>10690</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8522,7 +8522,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8542,7 +8542,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11102</t>
+          <t>10983</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8557,7 +8557,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1781710</t>
+          <t>1785724</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1897963</t>
+          <t>1901944</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>52,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>56,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1785960</t>
+          <t>1794112</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1907801</t>
+          <t>1911022</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8747,12 +8747,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>50,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>54,18%</t>
+          <t>54,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3613062</t>
+          <t>3602621</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3779327</t>
+          <t>3775337</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8782,12 +8782,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>52,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>54,83%</t>
+          <t>54,77%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>995526</t>
+          <t>989948</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1104732</t>
+          <t>1102799</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1088537</t>
+          <t>1083713</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1202739</t>
+          <t>1200692</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2103837</t>
+          <t>2112081</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2265466</t>
+          <t>2264554</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,85%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>350412</t>
+          <t>354460</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>427780</t>
+          <t>429988</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>404923</t>
+          <t>403075</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>486007</t>
+          <t>486084</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,7 +8973,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>781117</t>
+          <t>781235</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>894847</t>
+          <t>894670</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>55906</t>
+          <t>56931</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>90536</t>
+          <t>88866</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>50031</t>
+          <t>49936</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>82645</t>
+          <t>82767</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>113787</t>
+          <t>115180</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>162353</t>
+          <t>165172</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>12699</t>
+          <t>12061</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>31214</t>
+          <t>29511</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>9670</t>
+          <t>9900</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>27705</t>
+          <t>29850</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>26344</t>
+          <t>26729</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>51633</t>
+          <t>51930</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9234,7 +9234,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -9605,32 +9605,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>279631</t>
+          <t>310535</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>259840</t>
+          <t>290158</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>300239</t>
+          <t>333717</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>54,39%</t>
+          <t>53,75%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>50,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,4%</t>
+          <t>57,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9640,32 +9640,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>386965</t>
+          <t>414250</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>365857</t>
+          <t>391081</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>409722</t>
+          <t>435590</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>53,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9675,32 +9675,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>666596</t>
+          <t>724785</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>638087</t>
+          <t>688988</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>696965</t>
+          <t>756330</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,41%</t>
+          <t>49,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>54,2%</t>
         </is>
       </c>
     </row>
@@ -9718,32 +9718,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>134377</t>
+          <t>144232</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>114791</t>
+          <t>124598</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>151328</t>
+          <t>166031</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9753,32 +9753,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>212668</t>
+          <t>232771</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>192906</t>
+          <t>214844</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>232896</t>
+          <t>252186</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9788,32 +9788,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>347045</t>
+          <t>377002</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>319374</t>
+          <t>349180</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>374727</t>
+          <t>405172</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,04%</t>
         </is>
       </c>
     </row>
@@ -9831,32 +9831,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>53253</t>
+          <t>62659</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>42592</t>
+          <t>49967</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>66046</t>
+          <t>78748</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9866,32 +9866,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>88678</t>
+          <t>98180</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>76499</t>
+          <t>85445</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>103515</t>
+          <t>112442</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9901,32 +9901,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>141931</t>
+          <t>160839</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>126328</t>
+          <t>142599</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>160965</t>
+          <t>183393</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>13,14%</t>
         </is>
       </c>
     </row>
@@ -9944,32 +9944,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>32282</t>
+          <t>43494</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23699</t>
+          <t>32195</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42752</t>
+          <t>61842</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9979,32 +9979,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>47145</t>
+          <t>53453</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>38035</t>
+          <t>42199</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>61745</t>
+          <t>66146</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10014,32 +10014,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>79427</t>
+          <t>96947</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>66696</t>
+          <t>79894</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>93998</t>
+          <t>116716</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>8,36%</t>
         </is>
       </c>
     </row>
@@ -10057,32 +10057,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>14595</t>
+          <t>16795</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8796</t>
+          <t>10768</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21621</t>
+          <t>25215</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10092,32 +10092,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>16183</t>
+          <t>19002</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11185</t>
+          <t>13348</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>23518</t>
+          <t>27411</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10127,32 +10127,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>30778</t>
+          <t>35797</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>22251</t>
+          <t>27424</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>39713</t>
+          <t>45740</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -10170,17 +10170,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>514139</t>
+          <t>577716</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>514139</t>
+          <t>577716</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>514139</t>
+          <t>577716</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10205,17 +10205,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>751639</t>
+          <t>817656</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>751639</t>
+          <t>817656</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>751639</t>
+          <t>817656</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10240,17 +10240,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1265778</t>
+          <t>1395371</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1265778</t>
+          <t>1395371</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1265778</t>
+          <t>1395371</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10287,32 +10287,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1550855</t>
+          <t>1383633</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1440979</t>
+          <t>1332602</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1751840</t>
+          <t>1434607</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>62,11%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>62,99%</t>
+          <t>59,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>64,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10322,32 +10322,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1293900</t>
+          <t>1327045</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>966146</t>
+          <t>1282913</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1443304</t>
+          <t>1368658</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>61,16%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>59,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>63,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10357,32 +10357,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>2844755</t>
+          <t>2710678</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2487559</t>
+          <t>2645646</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3097399</t>
+          <t>2781379</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>62,88%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,99%</t>
+          <t>60,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>63,25%</t>
         </is>
       </c>
     </row>
@@ -10400,32 +10400,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>559748</t>
+          <t>641979</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>394475</t>
+          <t>595622</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>645196</t>
+          <t>688670</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10435,32 +10435,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>766903</t>
+          <t>634702</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>602236</t>
+          <t>599596</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1126868</t>
+          <t>676877</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10470,32 +10470,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1326651</t>
+          <t>1276681</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1113002</t>
+          <t>1218650</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1816966</t>
+          <t>1337992</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>30,43%</t>
         </is>
       </c>
     </row>
@@ -10513,32 +10513,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>98710</t>
+          <t>110262</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>71122</t>
+          <t>89465</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>123394</t>
+          <t>131402</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10548,32 +10548,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>106985</t>
+          <t>120727</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>80880</t>
+          <t>101885</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>132138</t>
+          <t>144329</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10583,32 +10583,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>205695</t>
+          <t>230989</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>163886</t>
+          <t>204072</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>242369</t>
+          <t>260783</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -10626,32 +10626,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>62709</t>
+          <t>73664</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42764</t>
+          <t>58328</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>81171</t>
+          <t>90790</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10661,32 +10661,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>57747</t>
+          <t>70655</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40041</t>
+          <t>56338</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>74494</t>
+          <t>85505</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10696,32 +10696,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>120456</t>
+          <t>144319</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>93948</t>
+          <t>123861</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>147273</t>
+          <t>166995</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -10739,32 +10739,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>15676</t>
+          <t>18324</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9360</t>
+          <t>11060</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26416</t>
+          <t>28451</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10774,32 +10774,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>10553</t>
+          <t>16532</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6413</t>
+          <t>10155</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>17292</t>
+          <t>25311</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
           <t>0,47%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10809,32 +10809,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>26228</t>
+          <t>34856</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>16923</t>
+          <t>24738</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>36999</t>
+          <t>47774</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -10852,17 +10852,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2287698</t>
+          <t>2227863</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2287698</t>
+          <t>2227863</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2287698</t>
+          <t>2227863</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10887,17 +10887,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2236087</t>
+          <t>2169660</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2236087</t>
+          <t>2169660</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2236087</t>
+          <t>2169660</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10922,17 +10922,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>4523785</t>
+          <t>4397524</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4523785</t>
+          <t>4397524</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4523785</t>
+          <t>4397524</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10969,32 +10969,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>446271</t>
+          <t>487591</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>420695</t>
+          <t>461312</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>470822</t>
+          <t>512991</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>68,52%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>64,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11004,32 +11004,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>479270</t>
+          <t>532136</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>460327</t>
+          <t>510613</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>498835</t>
+          <t>555258</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>69,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11039,22 +11039,22 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>925541</t>
+          <t>1019727</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>891256</t>
+          <t>986403</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>957133</t>
+          <t>1053039</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -11064,7 +11064,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>72,8%</t>
         </is>
       </c>
     </row>
@@ -11082,32 +11082,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>160546</t>
+          <t>176746</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>139775</t>
+          <t>154089</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>185860</t>
+          <t>202828</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11117,32 +11117,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>139911</t>
+          <t>155996</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>122358</t>
+          <t>137257</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>155760</t>
+          <t>176518</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11152,32 +11152,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>300457</t>
+          <t>332742</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>271272</t>
+          <t>304615</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>329704</t>
+          <t>362374</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,05%</t>
         </is>
       </c>
     </row>
@@ -11195,32 +11195,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>24808</t>
+          <t>26679</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17014</t>
+          <t>18072</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>35169</t>
+          <t>40794</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11230,32 +11230,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>29892</t>
+          <t>33595</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>21148</t>
+          <t>23965</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>43588</t>
+          <t>47133</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11265,32 +11265,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>54700</t>
+          <t>60274</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>41896</t>
+          <t>46669</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>71145</t>
+          <t>76193</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,27%</t>
         </is>
       </c>
     </row>
@@ -11308,32 +11308,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7678</t>
+          <t>13190</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4372</t>
+          <t>7525</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13829</t>
+          <t>21592</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11343,22 +11343,22 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6331</t>
+          <t>7140</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3534</t>
+          <t>3950</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11549</t>
+          <t>12393</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -11368,7 +11368,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11378,32 +11378,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>14008</t>
+          <t>20329</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9107</t>
+          <t>13003</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21091</t>
+          <t>31105</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -11421,32 +11421,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>7321</t>
+          <t>7381</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2864</t>
+          <t>2957</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14801</t>
+          <t>16082</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11456,22 +11456,22 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>5059</t>
+          <t>6010</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2415</t>
+          <t>2729</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9918</t>
+          <t>10751</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -11481,42 +11481,42 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>13391</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>7580</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>21728</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
           <t>1,5%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>12379</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>6975</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>20646</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -11534,17 +11534,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11569,17 +11569,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11604,17 +11604,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11651,32 +11651,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2276757</t>
+          <t>2181760</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2164799</t>
+          <t>2120191</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2551024</t>
+          <t>2241013</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>62,03%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>62,78%</t>
+          <t>60,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>73,98%</t>
+          <t>63,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11686,32 +11686,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2160135</t>
+          <t>2273431</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1757351</t>
+          <t>2220034</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2319759</t>
+          <t>2324029</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>59,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>62,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11721,32 +11721,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>4436892</t>
+          <t>4455191</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4009285</t>
+          <t>4369603</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4694795</t>
+          <t>4533235</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>61,54%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>56,5%</t>
+          <t>60,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>62,62%</t>
         </is>
       </c>
     </row>
@@ -11764,32 +11764,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>854672</t>
+          <t>962958</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>656109</t>
+          <t>903444</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>939500</t>
+          <t>1014848</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11799,32 +11799,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1119481</t>
+          <t>1023468</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>945795</t>
+          <t>976893</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1592272</t>
+          <t>1071372</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11834,32 +11834,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1974153</t>
+          <t>1986426</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1765463</t>
+          <t>1914567</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2538313</t>
+          <t>2060872</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>28,47%</t>
         </is>
       </c>
     </row>
@@ -11877,32 +11877,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>176771</t>
+          <t>199600</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>140465</t>
+          <t>173411</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>206732</t>
+          <t>226774</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11912,32 +11912,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>225555</t>
+          <t>252502</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>185762</t>
+          <t>225964</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>256992</t>
+          <t>281974</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11947,32 +11947,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>402327</t>
+          <t>452103</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>349176</t>
+          <t>416101</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>450448</t>
+          <t>498268</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -11990,32 +11990,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>102669</t>
+          <t>130347</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>77337</t>
+          <t>110725</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>123278</t>
+          <t>154820</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12025,32 +12025,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>111223</t>
+          <t>131248</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>90330</t>
+          <t>112952</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>132068</t>
+          <t>152654</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12060,32 +12060,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>213891</t>
+          <t>261595</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>178814</t>
+          <t>232386</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>242098</t>
+          <t>291552</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -12103,69 +12103,69 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>37591</t>
+          <t>42501</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>25241</t>
+          <t>30963</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>49748</t>
+          <t>56102</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>41544</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>31627</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>53470</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
           <t>1,44%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>31795</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>23042</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>41215</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>1,13%</t>
-        </is>
-      </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>112</t>
@@ -12173,32 +12173,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>69386</t>
+          <t>84045</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>55282</t>
+          <t>69270</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>88224</t>
+          <t>103555</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -12216,17 +12216,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3448460</t>
+          <t>3517166</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3448460</t>
+          <t>3517166</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3448460</t>
+          <t>3517166</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12251,17 +12251,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3648189</t>
+          <t>3722193</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3648189</t>
+          <t>3722193</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3648189</t>
+          <t>3722193</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12286,17 +12286,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7096649</t>
+          <t>7239359</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7096649</t>
+          <t>7239359</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7096649</t>
+          <t>7239359</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
